--- a/planilhas/precificacao/precificador/EXEMPLO.xlsx
+++ b/planilhas/precificacao/precificador/EXEMPLO.xlsx
@@ -23558,7 +23558,7 @@
         <v>164</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
@@ -23577,7 +23577,7 @@
       </c>
       <c r="C6" s="27">
         <f>IFERROR(MATCH($C$4,ProdNome,0),"")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -23586,7 +23586,7 @@
       </c>
       <c r="C8" s="30">
         <f>IF($C$6="","",IF(N(INDEX(Produtos!$K$5:$K$304,$C$6))&gt;0,INDEX(Produtos!$K$5:$K$304,$C$6),INDEX(Produtos!$O$5:$O$304,$C$6)))</f>
-        <v>44.9</v>
+        <v>83.9</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -23595,7 +23595,7 @@
       </c>
       <c r="C9" s="30">
         <f>IF($C$6="","",INDEX(Produtos!$L$5:$L$304,$C$6))</f>
-        <v>31.37</v>
+        <v>37.04</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -23613,7 +23613,7 @@
       </c>
       <c r="C11" s="30">
         <f>IF($C$6="","",C8*(1-C10)-C9)</f>
-        <v>-2.55916666666667</v>
+        <v>16.7958333333333</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -23622,7 +23622,7 @@
       </c>
       <c r="C12" s="30">
         <f>IF($C$6="","",C8*(1-$C$5))</f>
-        <v>40.41</v>
+        <v>75.51</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -23631,7 +23631,7 @@
       </c>
       <c r="C13" s="30">
         <f>IF($C$6="","",C12*(1-C10)-C9)</f>
-        <v>-5.44025000000001</v>
+        <v>11.41225</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -23640,16 +23640,16 @@
       </c>
       <c r="C14" s="31">
         <f>IF(OR($C$6="",N(C11)&lt;=0),"",1-C13/C11)</f>
-        <v>0</v>
+        <v>0.320530885636319</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="B15" s="14" t="s">
         <v>174</v>
       </c>
-      <c r="C15" s="32" t="str">
+      <c r="C15" s="32">
         <f>IF($C$6="","",IF(C13&lt;=0,"Impossível: dá prejuízo",IF(C11&lt;=0,"",C11/C13-1)))</f>
-        <v>Impossível: dá prejuízo</v>
+        <v>0.471737241414562</v>
       </c>
     </row>
     <row r="17" spans="2:6">
@@ -23684,19 +23684,19 @@
       </c>
       <c r="C19" s="23">
         <f>IF($C$6="","",$C$8*(1-B19))</f>
-        <v>44.9</v>
+        <v>83.9</v>
       </c>
       <c r="D19" s="23">
         <f>IF($C$6="","",C19*(1-$C$10)-$C$9)</f>
-        <v>-2.55916666666667</v>
+        <v>16.7958333333333</v>
       </c>
       <c r="E19" s="24">
         <f>IF(OR($C$6="",N($C$11)&lt;=0),"",1-D19/$C$11)</f>
         <v>0</v>
       </c>
-      <c r="F19" s="34" t="str">
+      <c r="F19" s="34">
         <f>IF($C$6="","",IF(D19&lt;=0,"Impossível",IF(N($C$11)&lt;=0,"",$C$11/D19-1)))</f>
-        <v>Impossível</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="2:6">
@@ -23705,19 +23705,19 @@
       </c>
       <c r="C20" s="23">
         <f>IF($C$6="","",$C$8*(1-B20))</f>
-        <v>42.655</v>
+        <v>79.705</v>
       </c>
       <c r="D20" s="23">
         <f>IF($C$6="","",C20*(1-$C$10)-$C$9)</f>
-        <v>-3.99970833333334</v>
+        <v>14.1040416666667</v>
       </c>
       <c r="E20" s="24">
         <f>IF(OR($C$6="",N($C$11)&lt;=0),"",1-D20/$C$11)</f>
-        <v>0</v>
-      </c>
-      <c r="F20" s="34" t="str">
+        <v>0.16026544281816</v>
+      </c>
+      <c r="F20" s="34">
         <f>IF($C$6="","",IF(D20&lt;=0,"Impossível",IF(N($C$11)&lt;=0,"",$C$11/D20-1)))</f>
-        <v>Impossível</v>
+        <v>0.190852503862664</v>
       </c>
     </row>
     <row r="21" spans="2:6">
@@ -23726,19 +23726,19 @@
       </c>
       <c r="C21" s="23">
         <f>IF($C$6="","",$C$8*(1-B21))</f>
-        <v>40.41</v>
+        <v>75.51</v>
       </c>
       <c r="D21" s="23">
         <f>IF($C$6="","",C21*(1-$C$10)-$C$9)</f>
-        <v>-5.44025000000001</v>
+        <v>11.41225</v>
       </c>
       <c r="E21" s="24">
         <f>IF(OR($C$6="",N($C$11)&lt;=0),"",1-D21/$C$11)</f>
-        <v>0</v>
-      </c>
-      <c r="F21" s="34" t="str">
+        <v>0.320530885636319</v>
+      </c>
+      <c r="F21" s="34">
         <f>IF($C$6="","",IF(D21&lt;=0,"Impossível",IF(N($C$11)&lt;=0,"",$C$11/D21-1)))</f>
-        <v>Impossível</v>
+        <v>0.471737241414562</v>
       </c>
     </row>
     <row r="22" spans="2:6">
@@ -23747,19 +23747,19 @@
       </c>
       <c r="C22" s="23">
         <f>IF($C$6="","",$C$8*(1-B22))</f>
-        <v>38.165</v>
+        <v>71.315</v>
       </c>
       <c r="D22" s="23">
         <f>IF($C$6="","",C22*(1-$C$10)-$C$9)</f>
-        <v>-6.88079166666667</v>
+        <v>8.72045833333333</v>
       </c>
       <c r="E22" s="24">
         <f>IF(OR($C$6="",N($C$11)&lt;=0),"",1-D22/$C$11)</f>
-        <v>0</v>
-      </c>
-      <c r="F22" s="34" t="str">
+        <v>0.480796328454478</v>
+      </c>
+      <c r="F22" s="34">
         <f>IF($C$6="","",IF(D22&lt;=0,"Impossível",IF(N($C$11)&lt;=0,"",$C$11/D22-1)))</f>
-        <v>Impossível</v>
+        <v>0.926026441653011</v>
       </c>
     </row>
     <row r="23" spans="2:6">
@@ -23768,19 +23768,19 @@
       </c>
       <c r="C23" s="23">
         <f>IF($C$6="","",$C$8*(1-B23))</f>
-        <v>35.92</v>
+        <v>67.12</v>
       </c>
       <c r="D23" s="23">
         <f>IF($C$6="","",C23*(1-$C$10)-$C$9)</f>
-        <v>-8.32133333333334</v>
+        <v>6.02866666666667</v>
       </c>
       <c r="E23" s="24">
         <f>IF(OR($C$6="",N($C$11)&lt;=0),"",1-D23/$C$11)</f>
-        <v>0</v>
-      </c>
-      <c r="F23" s="34" t="str">
+        <v>0.641061771272637</v>
+      </c>
+      <c r="F23" s="34">
         <f>IF($C$6="","",IF(D23&lt;=0,"Impossível",IF(N($C$11)&lt;=0,"",$C$11/D23-1)))</f>
-        <v>Impossível</v>
+        <v>1.78599469202698</v>
       </c>
     </row>
     <row r="24" spans="2:6">
@@ -23789,19 +23789,19 @@
       </c>
       <c r="C24" s="23">
         <f>IF($C$6="","",$C$8*(1-B24))</f>
-        <v>33.675</v>
+        <v>62.925</v>
       </c>
       <c r="D24" s="23">
         <f>IF($C$6="","",C24*(1-$C$10)-$C$9)</f>
-        <v>-9.761875</v>
+        <v>3.336875</v>
       </c>
       <c r="E24" s="24">
         <f>IF(OR($C$6="",N($C$11)&lt;=0),"",1-D24/$C$11)</f>
-        <v>0</v>
-      </c>
-      <c r="F24" s="34" t="str">
+        <v>0.801327214090796</v>
+      </c>
+      <c r="F24" s="34">
         <f>IF($C$6="","",IF(D24&lt;=0,"Impossível",IF(N($C$11)&lt;=0,"",$C$11/D24-1)))</f>
-        <v>Impossível</v>
+        <v>4.03340201036399</v>
       </c>
     </row>
     <row r="25" spans="2:6">
@@ -23810,19 +23810,19 @@
       </c>
       <c r="C25" s="23">
         <f>IF($C$6="","",$C$8*(1-B25))</f>
-        <v>31.43</v>
+        <v>58.73</v>
       </c>
       <c r="D25" s="23">
         <f>IF($C$6="","",C25*(1-$C$10)-$C$9)</f>
-        <v>-11.2024166666667</v>
+        <v>0.645083333333332</v>
       </c>
       <c r="E25" s="24">
         <f>IF(OR($C$6="",N($C$11)&lt;=0),"",1-D25/$C$11)</f>
-        <v>0</v>
-      </c>
-      <c r="F25" s="34" t="str">
+        <v>0.961592656908956</v>
+      </c>
+      <c r="F25" s="34">
         <f>IF($C$6="","",IF(D25&lt;=0,"Impossível",IF(N($C$11)&lt;=0,"",$C$11/D25-1)))</f>
-        <v>Impossível</v>
+        <v>25.0366877664385</v>
       </c>
     </row>
     <row r="27" spans="2:6">
